--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -38,10 +38,16 @@
     <t>name</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>desc</t>
   </si>
   <si>
-    <t>elements</t>
+    <t>elementA</t>
+  </si>
+  <si>
+    <t>elementB</t>
   </si>
   <si>
     <t>base_hp</t>
@@ -83,6 +89,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>PokemonTypeEnum</t>
+  </si>
+  <si>
     <t>ElementEnum</t>
   </si>
   <si>
@@ -101,6 +110,9 @@
     <t>名字(不填从id解析)</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -140,40 +152,16 @@
     <t>NO1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>怒潮龙是远古的巨龙后裔，拥有与元素共鸣的神奇力量，因此在面对冒犯自己的敌人时，它会毫不留情地倾泻自己的怒火，控制滔天的巨浪将敌人彻底淹没。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>怒潮龙有时候会在熟悉的伙伴面前咬住自己的尾巴不停地转圈，直到把自己转晕为止。这种行为与平行宇宙世界中一种叫做“猫猫”的神奇生物相似。</t>
-    </r>
+    <t>非玩家</t>
   </si>
   <si>
     <t>水</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>玩家</t>
   </si>
 </sst>
 </file>
@@ -916,13 +904,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1274,19 +1262,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="5" width="21.6339285714286" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.8839285714286" customWidth="1"/>
-    <col min="14" max="14" width="9.63392857142857" customWidth="1"/>
-    <col min="16" max="16" width="11.6339285714286" customWidth="1"/>
-    <col min="17" max="17" width="35.5" customWidth="1"/>
+    <col min="6" max="7" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="11.8839285714286" customWidth="1"/>
+    <col min="15" max="15" width="9.63392857142857" customWidth="1"/>
+    <col min="17" max="17" width="11.6339285714286" customWidth="1"/>
+    <col min="18" max="18" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,46 +1284,51 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,59 +1348,65 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1425,299 +1424,347 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-    </row>
-    <row r="5" ht="17.55" spans="1:17">
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" ht="17.55" spans="1:18">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:18">
+      <c r="B6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="9">
+        <v>340</v>
+      </c>
+      <c r="I6" s="9">
+        <v>450</v>
+      </c>
+      <c r="J6" s="13">
+        <v>65</v>
+      </c>
+      <c r="K6" s="13">
+        <v>90</v>
+      </c>
+      <c r="L6" s="14">
+        <v>40</v>
+      </c>
+      <c r="M6" s="14">
+        <v>80</v>
+      </c>
+      <c r="N6" s="17">
+        <v>100</v>
+      </c>
+      <c r="O6" s="17">
+        <v>160</v>
+      </c>
+      <c r="P6" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="18">
         <v>30</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" ht="17.55" spans="2:17">
-      <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="10">
+      <c r="R6" s="4"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:18">
+      <c r="B7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="9">
         <v>340</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I7" s="9">
         <v>450</v>
       </c>
-      <c r="I6" s="13">
+      <c r="J7" s="13">
         <v>65</v>
       </c>
-      <c r="J6" s="13">
+      <c r="K7" s="13">
         <v>90</v>
       </c>
-      <c r="K6" s="14">
+      <c r="L7" s="14">
         <v>40</v>
       </c>
-      <c r="L6" s="14">
+      <c r="M7" s="14">
         <v>80</v>
       </c>
-      <c r="M6" s="17">
+      <c r="N7" s="17">
         <v>100</v>
       </c>
-      <c r="N6" s="17">
+      <c r="O7" s="17">
         <v>160</v>
       </c>
-      <c r="O6" s="18">
+      <c r="P7" s="18">
         <v>0</v>
       </c>
-      <c r="P6" s="18">
+      <c r="Q7" s="18">
         <v>30</v>
       </c>
-      <c r="Q6" s="4"/>
-    </row>
-    <row r="7" spans="2:17">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="2:17">
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:18">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="13"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
+      <c r="K8" s="13"/>
       <c r="L8" s="14"/>
-      <c r="M8" s="17"/>
+      <c r="M8" s="14"/>
       <c r="N8" s="17"/>
-      <c r="O8" s="18"/>
+      <c r="O8" s="17"/>
       <c r="P8" s="18"/>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="2:17">
+      <c r="Q8" s="18"/>
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" ht="17.55" spans="2:18">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="13"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="14"/>
+      <c r="K9" s="13"/>
       <c r="L9" s="14"/>
-      <c r="M9" s="17"/>
+      <c r="M9" s="14"/>
       <c r="N9" s="17"/>
-      <c r="O9" s="18"/>
+      <c r="O9" s="17"/>
       <c r="P9" s="18"/>
-      <c r="Q9" s="4"/>
-    </row>
-    <row r="10" spans="2:17">
+      <c r="Q9" s="18"/>
+      <c r="R9" s="4"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:18">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="13"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
+      <c r="K10" s="13"/>
       <c r="L10" s="14"/>
-      <c r="M10" s="17"/>
+      <c r="M10" s="14"/>
       <c r="N10" s="17"/>
-      <c r="O10" s="18"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="18"/>
-      <c r="Q10" s="4"/>
-    </row>
-    <row r="11" spans="2:17">
+      <c r="Q10" s="18"/>
+      <c r="R10" s="4"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:18">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="13"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
+      <c r="K11" s="13"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="17"/>
+      <c r="M11" s="14"/>
       <c r="N11" s="17"/>
-      <c r="O11" s="18"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="18"/>
-      <c r="Q11" s="4"/>
-    </row>
-    <row r="12" spans="2:17">
+      <c r="Q11" s="18"/>
+      <c r="R11" s="4"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:18">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="13"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
+      <c r="K12" s="13"/>
       <c r="L12" s="14"/>
-      <c r="M12" s="17"/>
+      <c r="M12" s="14"/>
       <c r="N12" s="17"/>
-      <c r="O12" s="18"/>
+      <c r="O12" s="17"/>
       <c r="P12" s="18"/>
-      <c r="Q12" s="4"/>
-    </row>
-    <row r="13" spans="2:17">
+      <c r="Q12" s="18"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:18">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="13"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
+      <c r="K13" s="13"/>
       <c r="L13" s="14"/>
-      <c r="M13" s="17"/>
+      <c r="M13" s="14"/>
       <c r="N13" s="17"/>
-      <c r="O13" s="18"/>
+      <c r="O13" s="17"/>
       <c r="P13" s="18"/>
-      <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="2:17">
+      <c r="Q13" s="18"/>
+      <c r="R13" s="4"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:18">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="13"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
+      <c r="K14" s="13"/>
       <c r="L14" s="14"/>
-      <c r="M14" s="17"/>
+      <c r="M14" s="14"/>
       <c r="N14" s="17"/>
-      <c r="O14" s="18"/>
+      <c r="O14" s="17"/>
       <c r="P14" s="18"/>
-      <c r="Q14" s="4"/>
-    </row>
-    <row r="15" spans="2:17">
+      <c r="Q14" s="18"/>
+      <c r="R14" s="4"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:18">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="13"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
+      <c r="K15" s="13"/>
       <c r="L15" s="14"/>
-      <c r="M15" s="17"/>
+      <c r="M15" s="14"/>
       <c r="N15" s="17"/>
-      <c r="O15" s="18"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="18"/>
-      <c r="Q15" s="4"/>
-    </row>
-    <row r="16" spans="2:17">
+      <c r="Q15" s="18"/>
+      <c r="R15" s="4"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:18">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="13"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
+      <c r="K16" s="13"/>
       <c r="L16" s="14"/>
-      <c r="M16" s="17"/>
+      <c r="M16" s="14"/>
       <c r="N16" s="17"/>
-      <c r="O16" s="18"/>
+      <c r="O16" s="17"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="4"/>
-    </row>
-    <row r="17" spans="2:17">
+      <c r="Q16" s="18"/>
+      <c r="R16" s="4"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:18">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="13"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
+      <c r="K17" s="13"/>
       <c r="L17" s="14"/>
-      <c r="M17" s="17"/>
+      <c r="M17" s="14"/>
       <c r="N17" s="17"/>
-      <c r="O17" s="18"/>
+      <c r="O17" s="17"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="4"/>
     </row>
     <row r="18" ht="17.55" spans="2:2">
       <c r="B18" s="5"/>

--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35D622C-FA25-411A-AA78-7D7FA80B2CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon_table" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -162,19 +166,25 @@
   </si>
   <si>
     <t>玩家</t>
+  </si>
+  <si>
+    <t>raceA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>raceB</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RaceEnum</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,151 +207,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,13 +230,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799676503799554"/>
+        <fgColor theme="5" tint="0.79964598529007846"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399670400097659"/>
+        <fgColor theme="8" tint="0.39963988158818325"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,194 +270,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -639,253 +333,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -937,68 +389,28 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00F43308"/>
-      <color rgb="00FF8680"/>
+      <color rgb="FFF43308"/>
+      <color rgb="FFFF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1256,25 +668,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="21.6339285714286" customWidth="1"/>
-    <col min="6" max="7" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="11.8839285714286" customWidth="1"/>
-    <col min="15" max="15" width="9.63392857142857" customWidth="1"/>
-    <col min="17" max="17" width="11.6339285714286" customWidth="1"/>
-    <col min="18" max="18" width="35.5" customWidth="1"/>
+    <col min="3" max="5" width="21.625" customWidth="1"/>
+    <col min="6" max="9" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="17" max="17" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="11.625" customWidth="1"/>
+    <col min="20" max="20" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,39 +708,45 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,8 +767,10 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1372,11 +792,11 @@
       <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
+      <c r="H3" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
@@ -1402,9 +822,15 @@
       <c r="Q3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R3" s="1"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="R3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1425,8 +851,10 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-    </row>
-    <row r="5" ht="17.55" spans="1:18">
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1448,39 +876,41 @@
       <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="K5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="L5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="N5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="O5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="P5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="Q5" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="R5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="S5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" ht="17.55" spans="2:18">
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1497,39 +927,41 @@
       <c r="G6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9">
         <v>340</v>
       </c>
-      <c r="I6" s="9">
+      <c r="K6" s="9">
         <v>450</v>
       </c>
-      <c r="J6" s="13">
+      <c r="L6" s="13">
         <v>65</v>
       </c>
-      <c r="K6" s="13">
+      <c r="M6" s="13">
         <v>90</v>
       </c>
-      <c r="L6" s="14">
+      <c r="N6" s="14">
         <v>40</v>
       </c>
-      <c r="M6" s="14">
+      <c r="O6" s="14">
         <v>80</v>
       </c>
-      <c r="N6" s="17">
+      <c r="P6" s="17">
         <v>100</v>
       </c>
-      <c r="O6" s="17">
+      <c r="Q6" s="17">
         <v>160</v>
       </c>
-      <c r="P6" s="18">
+      <c r="R6" s="18">
         <v>0</v>
       </c>
-      <c r="Q6" s="18">
+      <c r="S6" s="18">
         <v>30</v>
       </c>
-      <c r="R6" s="4"/>
-    </row>
-    <row r="7" ht="17.55" spans="2:18">
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>44</v>
       </c>
@@ -1544,239 +976,261 @@
       <c r="G7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9">
         <v>340</v>
       </c>
-      <c r="I7" s="9">
+      <c r="K7" s="9">
         <v>450</v>
       </c>
-      <c r="J7" s="13">
+      <c r="L7" s="13">
         <v>65</v>
       </c>
-      <c r="K7" s="13">
+      <c r="M7" s="13">
         <v>90</v>
       </c>
-      <c r="L7" s="14">
+      <c r="N7" s="14">
         <v>40</v>
       </c>
-      <c r="M7" s="14">
+      <c r="O7" s="14">
         <v>80</v>
       </c>
-      <c r="N7" s="17">
+      <c r="P7" s="17">
         <v>100</v>
       </c>
-      <c r="O7" s="17">
+      <c r="Q7" s="17">
         <v>160</v>
       </c>
-      <c r="P7" s="18">
+      <c r="R7" s="18">
         <v>0</v>
       </c>
-      <c r="Q7" s="18">
+      <c r="S7" s="18">
         <v>30</v>
       </c>
-      <c r="R7" s="4"/>
-    </row>
-    <row r="8" ht="17.55" spans="2:18">
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" ht="17.55" spans="2:18">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="4"/>
-    </row>
-    <row r="10" ht="17.55" spans="2:18">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="4"/>
-    </row>
-    <row r="11" ht="17.55" spans="2:18">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="4"/>
-    </row>
-    <row r="12" ht="17.55" spans="2:18">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="4"/>
-    </row>
-    <row r="13" ht="17.55" spans="2:18">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="4"/>
-    </row>
-    <row r="14" ht="17.55" spans="2:18">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="4"/>
-    </row>
-    <row r="15" ht="17.55" spans="2:18">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="4"/>
-    </row>
-    <row r="16" ht="17.55" spans="2:18">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="4"/>
-    </row>
-    <row r="17" ht="17.55" spans="2:18">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="4"/>
-    </row>
-    <row r="18" ht="17.55" spans="2:2">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
     </row>
-    <row r="19" ht="17.55" spans="2:2">
+    <row r="19" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
     </row>
-    <row r="20" ht="17.55" spans="2:2">
+    <row r="20" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35D622C-FA25-411A-AA78-7D7FA80B2CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon_table" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -48,12 +44,21 @@
     <t>desc</t>
   </si>
   <si>
+    <t>passive</t>
+  </si>
+  <si>
     <t>elementA</t>
   </si>
   <si>
     <t>elementB</t>
   </si>
   <si>
+    <t>raceA</t>
+  </si>
+  <si>
+    <t>raceB</t>
+  </si>
+  <si>
     <t>base_hp</t>
   </si>
   <si>
@@ -96,9 +101,15 @@
     <t>PokemonTypeEnum</t>
   </si>
   <si>
+    <t>PassiveEnum</t>
+  </si>
+  <si>
     <t>ElementEnum</t>
   </si>
   <si>
+    <t>RaceEnum</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -120,6 +131,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>特性</t>
+  </si>
+  <si>
     <t>属性</t>
   </si>
   <si>
@@ -166,25 +180,19 @@
   </si>
   <si>
     <t>玩家</t>
-  </si>
-  <si>
-    <t>raceA</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>raceB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RaceEnum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +208,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
@@ -207,21 +222,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,13 +375,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79964598529007846"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39963988158818325"/>
+        <fgColor theme="5" tint="0.799645985290078"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399639881588183"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,8 +415,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -333,11 +664,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -353,22 +926,29 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -377,10 +957,10 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -389,28 +969,68 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFF43308"/>
-      <color rgb="FFFF8680"/>
+      <color rgb="00F43308"/>
+      <color rgb="00FF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -668,25 +1288,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="5" width="21.625" customWidth="1"/>
-    <col min="6" max="9" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
-    <col min="17" max="17" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="11.625" customWidth="1"/>
-    <col min="20" max="20" width="35.5" customWidth="1"/>
+    <col min="6" max="10" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="11.875" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="20" max="20" width="11.625" customWidth="1"/>
+    <col min="21" max="21" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,45 +1328,48 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,70 +1392,74 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -853,164 +1480,170 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" spans="2:21">
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="13">
+        <v>340</v>
+      </c>
+      <c r="L6" s="13">
+        <v>450</v>
+      </c>
+      <c r="M6" s="16">
+        <v>65</v>
+      </c>
+      <c r="N6" s="16">
+        <v>90</v>
+      </c>
+      <c r="O6" s="17">
+        <v>40</v>
+      </c>
+      <c r="P6" s="17">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>100</v>
+      </c>
+      <c r="R6" s="20">
+        <v>160</v>
+      </c>
+      <c r="S6" s="21">
+        <v>0</v>
+      </c>
+      <c r="T6" s="21">
         <v>30</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9">
-        <v>340</v>
-      </c>
-      <c r="K6" s="9">
-        <v>450</v>
-      </c>
-      <c r="L6" s="13">
-        <v>65</v>
-      </c>
-      <c r="M6" s="13">
-        <v>90</v>
-      </c>
-      <c r="N6" s="14">
-        <v>40</v>
-      </c>
-      <c r="O6" s="14">
-        <v>80</v>
-      </c>
-      <c r="P6" s="17">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>160</v>
-      </c>
-      <c r="R6" s="18">
-        <v>0</v>
-      </c>
-      <c r="S6" s="18">
-        <v>30</v>
-      </c>
-      <c r="T6" s="4"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U6" s="4"/>
+    </row>
+    <row r="7" spans="2:21">
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="9">
+      <c r="J7" s="8"/>
+      <c r="K7" s="13">
         <v>340</v>
       </c>
-      <c r="K7" s="9">
+      <c r="L7" s="13">
         <v>450</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="16">
         <v>65</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="16">
         <v>90</v>
       </c>
-      <c r="N7" s="14">
+      <c r="O7" s="17">
         <v>40</v>
       </c>
-      <c r="O7" s="14">
+      <c r="P7" s="17">
         <v>80</v>
       </c>
-      <c r="P7" s="17">
+      <c r="Q7" s="20">
         <v>100</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="R7" s="20">
         <v>160</v>
       </c>
-      <c r="R7" s="18">
+      <c r="S7" s="21">
         <v>0</v>
       </c>
-      <c r="S7" s="18">
+      <c r="T7" s="21">
         <v>30</v>
       </c>
-      <c r="T7" s="4"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U7" s="4"/>
+    </row>
+    <row r="8" spans="2:21">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1019,19 +1652,20 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="13"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="17"/>
       <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="4"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="4"/>
+    </row>
+    <row r="9" spans="2:21">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1040,19 +1674,20 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="13"/>
       <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="17"/>
       <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="4"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="4"/>
+    </row>
+    <row r="10" spans="2:21">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1061,19 +1696,20 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="13"/>
       <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="4"/>
-    </row>
-    <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="4"/>
+    </row>
+    <row r="11" spans="2:21">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1082,19 +1718,20 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="13"/>
       <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="17"/>
       <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="4"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="4"/>
+    </row>
+    <row r="12" spans="2:21">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1103,19 +1740,20 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="13"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="17"/>
       <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="4"/>
-    </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="4"/>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1124,19 +1762,20 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="13"/>
       <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="17"/>
       <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="4"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="4"/>
+    </row>
+    <row r="14" spans="2:21">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1145,19 +1784,20 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="13"/>
       <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="17"/>
       <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="4"/>
-    </row>
-    <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="4"/>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1166,19 +1806,20 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="13"/>
       <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="4"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="4"/>
+    </row>
+    <row r="16" spans="2:21">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1187,19 +1828,20 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="13"/>
       <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="17"/>
       <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="4"/>
-    </row>
-    <row r="17" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="4"/>
+    </row>
+    <row r="17" spans="2:21">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1208,29 +1850,30 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="13"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="17"/>
       <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="4"/>
-    </row>
-    <row r="18" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" spans="2:2">
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="28000" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -167,10 +167,7 @@
     <t>最大适应力</t>
   </si>
   <si>
-    <t>NO1</t>
-  </si>
-  <si>
-    <t>非玩家</t>
+    <t>玩家</t>
   </si>
   <si>
     <t>水</t>
@@ -179,7 +176,10 @@
     <t>None</t>
   </si>
   <si>
-    <t>玩家</t>
+    <t>测试0</t>
+  </si>
+  <si>
+    <t>普通</t>
   </si>
 </sst>
 </file>
@@ -192,7 +192,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,13 +202,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -632,7 +625,9 @@
       <right style="medium">
         <color rgb="FFDEE0E3"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
@@ -645,9 +640,7 @@
       <right style="medium">
         <color rgb="FFDEE0E3"/>
       </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
@@ -780,194 +773,191 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1331,10 +1321,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1419,10 +1409,10 @@
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -1482,7 +1472,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" ht="17.55" spans="1:21">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1498,379 +1488,377 @@
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="11" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="Q5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="18" t="s">
+      <c r="R5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="19" t="s">
+      <c r="T5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="U5" s="3"/>
-    </row>
-    <row r="6" spans="2:21">
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:21">
       <c r="B6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="11">
+        <v>340</v>
+      </c>
+      <c r="L6" s="11">
+        <v>450</v>
+      </c>
+      <c r="M6" s="14">
+        <v>65</v>
+      </c>
+      <c r="N6" s="14">
+        <v>90</v>
+      </c>
+      <c r="O6" s="15">
+        <v>40</v>
+      </c>
+      <c r="P6" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>100</v>
+      </c>
+      <c r="R6" s="18">
+        <v>160</v>
+      </c>
+      <c r="S6" s="19">
+        <v>0</v>
+      </c>
+      <c r="T6" s="19">
+        <v>30</v>
+      </c>
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:21">
+      <c r="B7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="13">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="11">
         <v>340</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L7" s="11">
         <v>450</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M7" s="14">
         <v>65</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N7" s="14">
         <v>90</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O7" s="15">
         <v>40</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P7" s="15">
         <v>80</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q7" s="18">
         <v>100</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R7" s="18">
         <v>160</v>
       </c>
-      <c r="S6" s="21">
+      <c r="S7" s="19">
         <v>0</v>
       </c>
-      <c r="T6" s="21">
+      <c r="T7" s="19">
         <v>30</v>
       </c>
-      <c r="U6" s="4"/>
-    </row>
-    <row r="7" spans="2:21">
-      <c r="B7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="13">
-        <v>340</v>
-      </c>
-      <c r="L7" s="13">
-        <v>450</v>
-      </c>
-      <c r="M7" s="16">
-        <v>65</v>
-      </c>
-      <c r="N7" s="16">
-        <v>90</v>
-      </c>
-      <c r="O7" s="17">
-        <v>40</v>
-      </c>
-      <c r="P7" s="17">
-        <v>80</v>
-      </c>
-      <c r="Q7" s="20">
-        <v>100</v>
-      </c>
-      <c r="R7" s="20">
-        <v>160</v>
-      </c>
-      <c r="S7" s="21">
-        <v>0</v>
-      </c>
-      <c r="T7" s="21">
-        <v>30</v>
-      </c>
-      <c r="U7" s="4"/>
-    </row>
-    <row r="8" spans="2:21">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="4"/>
-    </row>
-    <row r="9" spans="2:21">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="4"/>
-    </row>
-    <row r="10" spans="2:21">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="4"/>
-    </row>
-    <row r="11" spans="2:21">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="4"/>
-    </row>
-    <row r="12" spans="2:21">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="4"/>
-    </row>
-    <row r="13" spans="2:21">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="4"/>
-    </row>
-    <row r="14" spans="2:21">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="4"/>
-    </row>
-    <row r="15" spans="2:21">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="4"/>
-    </row>
-    <row r="16" spans="2:21">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" spans="2:21">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
+      <c r="U7" s="3"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:21">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" ht="17.55" spans="2:21">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:21">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:21">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:21">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="3"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:21">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:21">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="3"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:21">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:21">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:21">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="3"/>
+    </row>
+    <row r="18" ht="17.55" spans="2:2">
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" ht="17.55" spans="2:2">
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" ht="17.55" spans="2:2">
+      <c r="B20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="12920"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="122">
   <si>
     <t>##var</t>
   </si>
@@ -59,34 +59,79 @@
     <t>raceB</t>
   </si>
   <si>
-    <t>base_hp</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>base_atk</t>
-  </si>
-  <si>
-    <t>max_atk</t>
-  </si>
-  <si>
-    <t>base_def</t>
-  </si>
-  <si>
-    <t>max_def</t>
-  </si>
-  <si>
-    <t>base_speed</t>
-  </si>
-  <si>
-    <t>max_speed</t>
-  </si>
-  <si>
-    <t>base_adap</t>
-  </si>
-  <si>
-    <t>max_adap</t>
+    <t>lv1_hp</t>
+  </si>
+  <si>
+    <t>lv2_hp</t>
+  </si>
+  <si>
+    <t>lv3_hp</t>
+  </si>
+  <si>
+    <t>lv4_hp</t>
+  </si>
+  <si>
+    <t>lv5_hp</t>
+  </si>
+  <si>
+    <t>lv1_atk</t>
+  </si>
+  <si>
+    <t>lv2_atk</t>
+  </si>
+  <si>
+    <t>lv3_atk</t>
+  </si>
+  <si>
+    <t>lv4_atk</t>
+  </si>
+  <si>
+    <t>lv5_atk</t>
+  </si>
+  <si>
+    <t>lv1_def</t>
+  </si>
+  <si>
+    <t>lv2_def</t>
+  </si>
+  <si>
+    <t>lv3_def</t>
+  </si>
+  <si>
+    <t>lv4_def</t>
+  </si>
+  <si>
+    <t>lv5_def</t>
+  </si>
+  <si>
+    <t>lv1_speed</t>
+  </si>
+  <si>
+    <t>lv2_speed</t>
+  </si>
+  <si>
+    <t>lv3_speed</t>
+  </si>
+  <si>
+    <t>lv4_speed</t>
+  </si>
+  <si>
+    <t>lv5_speed</t>
+  </si>
+  <si>
+    <t>lv1_adap</t>
+  </si>
+  <si>
+    <t>lv2_adap</t>
+  </si>
+  <si>
+    <t>lv3_adap</t>
+  </si>
+  <si>
+    <t>lv4_adap</t>
+  </si>
+  <si>
+    <t>lv5_adap</t>
   </si>
   <si>
     <t>##type</t>
@@ -131,55 +176,223 @@
     <t>描述</t>
   </si>
   <si>
-    <t>特性</t>
+    <t>特点</t>
+  </si>
+  <si>
+    <t>特点描述</t>
   </si>
   <si>
     <t>属性</t>
   </si>
   <si>
-    <t>基础生命值</t>
-  </si>
-  <si>
-    <t>最大生命值</t>
-  </si>
-  <si>
-    <t>基础攻击力</t>
-  </si>
-  <si>
-    <t>最大攻击力</t>
-  </si>
-  <si>
-    <t>基础防御力</t>
-  </si>
-  <si>
-    <t>最大防御力</t>
-  </si>
-  <si>
-    <t>基础速度</t>
-  </si>
-  <si>
-    <t>最大速度</t>
-  </si>
-  <si>
-    <t>基础适应力</t>
-  </si>
-  <si>
-    <t>最大适应力</t>
+    <t>1级生命</t>
+  </si>
+  <si>
+    <t>2级生命</t>
+  </si>
+  <si>
+    <t>3级生命</t>
+  </si>
+  <si>
+    <t>4级生命</t>
+  </si>
+  <si>
+    <t>5级生命</t>
+  </si>
+  <si>
+    <t>1级力量</t>
+  </si>
+  <si>
+    <t>2级力量</t>
+  </si>
+  <si>
+    <t>3级力量</t>
+  </si>
+  <si>
+    <t>4级力量</t>
+  </si>
+  <si>
+    <t>5级力量</t>
+  </si>
+  <si>
+    <t>1级防御</t>
+  </si>
+  <si>
+    <t>2级防御</t>
+  </si>
+  <si>
+    <t>3级防御</t>
+  </si>
+  <si>
+    <t>4级防御</t>
+  </si>
+  <si>
+    <t>5级防御</t>
+  </si>
+  <si>
+    <t>1级速度</t>
+  </si>
+  <si>
+    <t>2级速度</t>
+  </si>
+  <si>
+    <t>3级速度</t>
+  </si>
+  <si>
+    <t>4级速度</t>
+  </si>
+  <si>
+    <t>5级速度</t>
+  </si>
+  <si>
+    <t>1级适应</t>
+  </si>
+  <si>
+    <t>2级适应</t>
+  </si>
+  <si>
+    <t>3级适应</t>
+  </si>
+  <si>
+    <t>4级适应</t>
+  </si>
+  <si>
+    <t>5级适应</t>
   </si>
   <si>
     <t>玩家</t>
   </si>
   <si>
-    <t>水</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
-    <t>测试0</t>
+    <t>灯笼鬼</t>
   </si>
   <si>
     <t>普通</t>
+  </si>
+  <si>
+    <t>捡拾</t>
+  </si>
+  <si>
+    <t>战斗中，灯笼鬼的攻击造成的伤害改为30%，并且每次攻击都能够获得1-3个水晶。当你拥有的水晶数量不小于50时，灯笼鬼的攻击会使敌人获得“易损“状态。</t>
+  </si>
+  <si>
+    <t>Ghost</t>
+  </si>
+  <si>
+    <t>小幽魂</t>
+  </si>
+  <si>
+    <t>水晶诅咒</t>
+  </si>
+  <si>
+    <t>战斗中无法攻击。己方怪兽攻击4次后，对所有敌方单位造成当前你拥有的水晶数量的50%的伤害。</t>
+  </si>
+  <si>
+    <t>笨笨甲熊</t>
+  </si>
+  <si>
+    <t>常规机械</t>
+  </si>
+  <si>
+    <t>笨笨甲熊不受任何负面效果影响。在每次精英或Boss战斗结束后，笨笨甲熊随机从“暴虐”“吸血”“肉质”效果中获取一种，每种效果最多获取一次。</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>枯木妖</t>
+  </si>
+  <si>
+    <t>枯木逢春</t>
+  </si>
+  <si>
+    <t>战斗开始时，使所有敌方怪兽获得一层“寄生”效果。当敌方怪兽的“寄生”效果层数达到上限，且该怪兽将要获得“寄生”效果时，改为使该敌方怪兽具有的“寄生”效果伤害增加1点。</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>烈火领主</t>
+  </si>
+  <si>
+    <t>高温</t>
+  </si>
+  <si>
+    <t>烈火领主的攻击能使目标敌方怪兽获得一层“灼伤”效果。</t>
+  </si>
+  <si>
+    <t>Spirit</t>
+  </si>
+  <si>
+    <t>落叶蝴蝶</t>
+  </si>
+  <si>
+    <t>下毒</t>
+  </si>
+  <si>
+    <t>敌方怪兽的“寄生”效果不会治疗己方单位，改为敌方怪兽具有的“寄生”效果造成2倍高额伤害。</t>
+  </si>
+  <si>
+    <t>Insect</t>
+  </si>
+  <si>
+    <t>一口鲸</t>
+  </si>
+  <si>
+    <t>大口吃</t>
+  </si>
+  <si>
+    <t>一口鲸的防御永久为0。战斗结束后，使一口鲸的最大生命永久提升5点。若一口鲸通过特点获得的最大生命不小于100点，则额外随机从“暴虐”“吸血”“肉质”效果中获取一种，每种效果最多获取一次。</t>
+  </si>
+  <si>
+    <t>铁刀客</t>
+  </si>
+  <si>
+    <t>一刀斩</t>
+  </si>
+  <si>
+    <t>铁刀客每具有一层“升级”效果，铁刀客攻击时便有5%的几率造成1.3倍高额伤害。</t>
+  </si>
+  <si>
+    <t>围巾狸</t>
+  </si>
+  <si>
+    <t>屯屯</t>
+  </si>
+  <si>
+    <t>战斗中，围巾狸每存活2个回合，便获得一层“储藏”效果。</t>
+  </si>
+  <si>
+    <t>研究体0号</t>
+  </si>
+  <si>
+    <t>仇恨滔天</t>
+  </si>
+  <si>
+    <t>研究体0号攻击只能造成50%的伤害，但能够同时攻击至多5个敌方怪兽。如果研究体0号具有“升级”效果，则此特点改为：消耗一层“升级”效果，研究体0号攻击能造成150%的高额伤害，并且能够同时攻击至多5个敌方怪兽。</t>
+  </si>
+  <si>
+    <t>猛毒蝎</t>
+  </si>
+  <si>
+    <t>猛毒</t>
+  </si>
+  <si>
+    <t>猛毒蝎的攻击能够使目标敌方怪兽获得一层“神经毒素”效果。</t>
+  </si>
+  <si>
+    <t>负树龟</t>
+  </si>
+  <si>
+    <t>负重前行</t>
+  </si>
+  <si>
+    <t>当有敌方怪兽因“寄生”效果受到伤害时，负树龟的最大防御永久提升1点。负树龟攻击造成的伤害额外增加其防御力的10%。</t>
   </si>
 </sst>
 </file>
@@ -359,7 +572,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,6 +593,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9F5D6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -595,7 +814,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -642,6 +861,21 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
@@ -779,7 +1013,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -791,169 +1025,190 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1284,19 +1539,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AK20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="5" width="21.625" customWidth="1"/>
-    <col min="6" max="10" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="11.625" customWidth="1"/>
-    <col min="21" max="21" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="67.5833333333333" customWidth="1"/>
+    <col min="8" max="11" width="13.5" customWidth="1"/>
+    <col min="27" max="27" width="11.875" customWidth="1"/>
+    <col min="28" max="31" width="9.625" customWidth="1"/>
+    <col min="33" max="36" width="11.625" customWidth="1"/>
+    <col min="37" max="37" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1316,50 +1573,98 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1"/>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:37">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1383,73 +1688,137 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:37">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK3" s="1"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:37">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1471,394 +1840,877 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:21">
+    <row r="5" ht="14.75" spans="1:37">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="U5" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="X5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y5" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z5" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA5" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB5" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC5" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD5" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE5" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF5" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG5" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH5" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI5" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ5" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" s="27"/>
+    </row>
+    <row r="6" ht="14.75" spans="2:37">
+      <c r="B6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="13">
+        <v>340</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13">
+        <v>450</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>65</v>
+      </c>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21">
+        <v>90</v>
+      </c>
+      <c r="V6" s="22">
+        <v>40</v>
+      </c>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22">
+        <v>80</v>
+      </c>
+      <c r="AA6" s="25">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25">
+        <v>160</v>
+      </c>
+      <c r="AF6" s="26">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="26"/>
+      <c r="AH6" s="26"/>
+      <c r="AI6" s="26"/>
+      <c r="AJ6" s="26">
         <v>30</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="13" t="s">
+      <c r="AK6" s="4"/>
+    </row>
+    <row r="7" ht="14.75" spans="2:37">
+      <c r="B7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13">
+        <v>340</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13">
+        <v>450</v>
+      </c>
+      <c r="Q7" s="21">
+        <v>65</v>
+      </c>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21">
+        <v>90</v>
+      </c>
+      <c r="V7" s="22">
         <v>40</v>
       </c>
-      <c r="P5" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="S5" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="T5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="20"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22">
+        <v>80</v>
+      </c>
+      <c r="AA7" s="25">
+        <v>100</v>
+      </c>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25">
+        <v>160</v>
+      </c>
+      <c r="AF7" s="26">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="26"/>
+      <c r="AJ7" s="26">
+        <v>30</v>
+      </c>
+      <c r="AK7" s="4"/>
     </row>
-    <row r="6" ht="17.55" spans="2:21">
-      <c r="B6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="11">
-        <v>340</v>
-      </c>
-      <c r="L6" s="11">
-        <v>450</v>
-      </c>
-      <c r="M6" s="14">
-        <v>65</v>
-      </c>
-      <c r="N6" s="14">
+    <row r="8" ht="14.75" spans="2:37">
+      <c r="B8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="26"/>
+      <c r="AJ8" s="26"/>
+      <c r="AK8" s="4"/>
+    </row>
+    <row r="9" ht="14.75" spans="2:37">
+      <c r="B9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="15">
-        <v>40</v>
-      </c>
-      <c r="P6" s="15">
+      <c r="K9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="4"/>
+    </row>
+    <row r="10" ht="14.75" spans="2:37">
+      <c r="B10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Q6" s="18">
+      <c r="E10" s="4"/>
+      <c r="F10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="17"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="26"/>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="4"/>
+    </row>
+    <row r="11" ht="14.75" spans="2:37">
+      <c r="B11" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="17"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="26"/>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="4"/>
+    </row>
+    <row r="12" ht="14.75" spans="2:37">
+      <c r="B12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="R6" s="18">
-        <v>160</v>
-      </c>
-      <c r="S6" s="19">
-        <v>0</v>
-      </c>
-      <c r="T6" s="19">
-        <v>30</v>
-      </c>
-      <c r="U6" s="3"/>
+      <c r="C12" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="26"/>
+      <c r="AJ12" s="26"/>
+      <c r="AK12" s="4"/>
     </row>
-    <row r="7" ht="17.55" spans="2:21">
-      <c r="B7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="11">
-        <v>340</v>
-      </c>
-      <c r="L7" s="11">
-        <v>450</v>
-      </c>
-      <c r="M7" s="14">
-        <v>65</v>
-      </c>
-      <c r="N7" s="14">
+    <row r="13" ht="14.75" spans="2:37">
+      <c r="B13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="O7" s="15">
-        <v>40</v>
-      </c>
-      <c r="P7" s="15">
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="26"/>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="4"/>
+    </row>
+    <row r="14" ht="14.75" spans="2:37">
+      <c r="B14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="18">
-        <v>100</v>
-      </c>
-      <c r="R7" s="18">
-        <v>160</v>
-      </c>
-      <c r="S7" s="19">
-        <v>0</v>
-      </c>
-      <c r="T7" s="19">
-        <v>30</v>
-      </c>
-      <c r="U7" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="26"/>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="4"/>
     </row>
-    <row r="8" ht="17.55" spans="2:21">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="3"/>
+    <row r="15" ht="14.75" spans="2:37">
+      <c r="B15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="26"/>
+      <c r="AJ15" s="26"/>
+      <c r="AK15" s="4"/>
     </row>
-    <row r="9" ht="17.55" spans="2:21">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="3"/>
+    <row r="16" ht="14.75" spans="2:37">
+      <c r="B16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="26"/>
+      <c r="AJ16" s="26"/>
+      <c r="AK16" s="4"/>
     </row>
-    <row r="10" ht="17.55" spans="2:21">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="3"/>
+    <row r="17" ht="14.75" spans="2:37">
+      <c r="B17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K17" s="17"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="26"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="26"/>
+      <c r="AJ17" s="26"/>
+      <c r="AK17" s="4"/>
     </row>
-    <row r="11" ht="17.55" spans="2:21">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="3"/>
+    <row r="18" ht="14.75" spans="2:36">
+      <c r="B18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="26"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="26"/>
+      <c r="AJ18" s="26"/>
     </row>
-    <row r="12" ht="17.55" spans="2:21">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="3"/>
+    <row r="19" ht="14.75" spans="2:11">
+      <c r="B19" s="9"/>
+      <c r="K19" s="18"/>
     </row>
-    <row r="13" ht="17.55" spans="2:21">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="3"/>
-    </row>
-    <row r="14" ht="17.55" spans="2:21">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="3"/>
-    </row>
-    <row r="15" ht="17.55" spans="2:21">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="3"/>
-    </row>
-    <row r="16" ht="17.55" spans="2:21">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="3"/>
-    </row>
-    <row r="17" ht="17.55" spans="2:21">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="3"/>
-    </row>
-    <row r="18" ht="17.55" spans="2:2">
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" ht="17.55" spans="2:2">
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" ht="17.55" spans="2:2">
-      <c r="B20" s="4"/>
+    <row r="20" ht="14.75" spans="2:2">
+      <c r="B20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -41,12 +41,12 @@
     <t>type</t>
   </si>
   <si>
+    <t>passive</t>
+  </si>
+  <si>
     <t>desc</t>
   </si>
   <si>
-    <t>passive</t>
-  </si>
-  <si>
     <t>elementA</t>
   </si>
   <si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>类型</t>
-  </si>
-  <si>
-    <t>描述</t>
   </si>
   <si>
     <t>特点</t>
@@ -1137,7 +1134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1156,9 +1153,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1169,9 +1163,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1187,13 +1187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1539,21 +1533,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="21.625" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="67.5833333333333" customWidth="1"/>
-    <col min="8" max="11" width="13.5" customWidth="1"/>
-    <col min="27" max="27" width="11.875" customWidth="1"/>
-    <col min="28" max="31" width="9.625" customWidth="1"/>
-    <col min="33" max="36" width="11.625" customWidth="1"/>
-    <col min="37" max="37" width="35.5" customWidth="1"/>
+    <col min="3" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="67.5833333333333" customWidth="1"/>
+    <col min="7" max="10" width="13.5" customWidth="1"/>
+    <col min="26" max="26" width="11.875" customWidth="1"/>
+    <col min="27" max="30" width="9.625" customWidth="1"/>
+    <col min="32" max="35" width="11.625" customWidth="1"/>
+    <col min="36" max="36" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1573,98 +1567,95 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1"/>
+      <c r="AJ1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:36">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1703,9 +1694,8 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:36">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
@@ -1719,25 +1709,25 @@
         <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>41</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>42</v>
@@ -1811,12 +1801,9 @@
       <c r="AI3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AJ3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK3" s="1"/>
+      <c r="AJ3" s="1"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:36">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1855,9 +1842,8 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
     </row>
-    <row r="5" ht="14.75" spans="1:37">
+    <row r="5" spans="1:36">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -1870,7 +1856,7 @@
       <c r="D5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1880,41 +1866,41 @@
         <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="11" t="s">
         <v>55</v>
       </c>
       <c r="P5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="19" t="s">
+      <c r="R5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="T5" s="19" t="s">
+      <c r="T5" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="20" t="s">
         <v>61</v>
       </c>
       <c r="V5" s="20" t="s">
@@ -1929,788 +1915,773 @@
       <c r="Y5" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="Z5" s="20" t="s">
+      <c r="Z5" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="AB5" s="23" t="s">
+      <c r="AB5" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AD5" s="22" t="s">
         <v>70</v>
       </c>
       <c r="AE5" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AF5" s="24" t="s">
+      <c r="AF5" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="AG5" s="24" t="s">
+      <c r="AG5" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="AH5" s="24" t="s">
+      <c r="AH5" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="AI5" s="24" t="s">
+      <c r="AI5" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AJ5" s="24" t="s">
+      <c r="AJ5" s="26"/>
+    </row>
+    <row r="6" spans="2:36">
+      <c r="B6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AK5" s="27"/>
-    </row>
-    <row r="6" ht="14.75" spans="2:37">
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="L6" s="13">
+      <c r="K6" s="13">
         <v>340</v>
       </c>
+      <c r="L6" s="13"/>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13">
+      <c r="O6" s="13">
         <v>450</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="P6" s="14">
         <v>65</v>
       </c>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14">
+        <v>90</v>
+      </c>
       <c r="U6" s="21">
-        <v>90</v>
-      </c>
-      <c r="V6" s="22">
         <v>40</v>
       </c>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22">
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21">
         <v>80</v>
       </c>
-      <c r="AA6" s="25">
+      <c r="Z6" s="24">
         <v>100</v>
       </c>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="25"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24">
+        <v>160</v>
+      </c>
       <c r="AE6" s="25">
-        <v>160</v>
-      </c>
-      <c r="AF6" s="26">
         <v>0</v>
       </c>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="26"/>
-      <c r="AJ6" s="26">
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
+      <c r="AH6" s="25"/>
+      <c r="AI6" s="25">
         <v>30</v>
       </c>
-      <c r="AK6" s="4"/>
+      <c r="AJ6" s="4"/>
     </row>
-    <row r="7" ht="14.75" spans="2:37">
+    <row r="7" spans="2:36">
       <c r="B7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13">
+      <c r="J7" s="16"/>
+      <c r="K7" s="13">
         <v>340</v>
       </c>
+      <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13">
+      <c r="O7" s="13">
         <v>450</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="P7" s="14">
         <v>65</v>
       </c>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14">
+        <v>90</v>
+      </c>
       <c r="U7" s="21">
-        <v>90</v>
-      </c>
-      <c r="V7" s="22">
         <v>40</v>
       </c>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22">
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21">
         <v>80</v>
       </c>
-      <c r="AA7" s="25">
+      <c r="Z7" s="24">
         <v>100</v>
       </c>
-      <c r="AB7" s="25"/>
-      <c r="AC7" s="25"/>
-      <c r="AD7" s="25"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24">
+        <v>160</v>
+      </c>
       <c r="AE7" s="25">
-        <v>160</v>
-      </c>
-      <c r="AF7" s="26">
         <v>0</v>
       </c>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="26"/>
-      <c r="AJ7" s="26">
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="25">
         <v>30</v>
       </c>
-      <c r="AK7" s="4"/>
+      <c r="AJ7" s="4"/>
     </row>
-    <row r="8" ht="14.75" spans="2:37">
+    <row r="8" spans="2:36">
       <c r="B8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>86</v>
+      <c r="G8" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="15"/>
+        <v>77</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="16"/>
+      <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
       <c r="U8" s="21"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
       <c r="AE8" s="25"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="26"/>
-      <c r="AJ8" s="26"/>
-      <c r="AK8" s="4"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="4"/>
     </row>
-    <row r="9" ht="14.75" spans="2:37">
+    <row r="9" spans="2:36">
       <c r="B9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>91</v>
-      </c>
+      <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
       <c r="U9" s="21"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
       <c r="AE9" s="25"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="4"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="4"/>
     </row>
-    <row r="10" ht="14.75" spans="2:37">
+    <row r="10" spans="2:36">
       <c r="B10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="K10" s="17"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
       <c r="U10" s="21"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
       <c r="AE10" s="25"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="26"/>
-      <c r="AJ10" s="26"/>
-      <c r="AK10" s="4"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="4"/>
     </row>
-    <row r="11" ht="14.75" spans="2:37">
+    <row r="11" spans="2:36">
       <c r="B11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="17"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
       <c r="U11" s="21"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
       <c r="AE11" s="25"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="26"/>
-      <c r="AJ11" s="26"/>
-      <c r="AK11" s="4"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="4"/>
     </row>
-    <row r="12" ht="14.75" spans="2:37">
+    <row r="12" spans="2:36">
       <c r="B12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>103</v>
-      </c>
+      <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
       <c r="U12" s="21"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
       <c r="AE12" s="25"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="26"/>
-      <c r="AI12" s="26"/>
-      <c r="AJ12" s="26"/>
-      <c r="AK12" s="4"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="4"/>
     </row>
-    <row r="13" ht="14.75" spans="2:37">
+    <row r="13" spans="2:36">
       <c r="B13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>106</v>
+      <c r="G13" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>90</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
       <c r="U13" s="21"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="25"/>
-      <c r="AC13" s="25"/>
-      <c r="AD13" s="25"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
       <c r="AE13" s="25"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="26"/>
-      <c r="AJ13" s="26"/>
-      <c r="AK13" s="4"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="25"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="4"/>
     </row>
-    <row r="14" ht="14.75" spans="2:37">
+    <row r="14" spans="2:36">
       <c r="B14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="4"/>
       <c r="F14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>109</v>
+      <c r="G14" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>91</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
       <c r="U14" s="21"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="25"/>
-      <c r="AC14" s="25"/>
-      <c r="AD14" s="25"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
       <c r="AE14" s="25"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="26"/>
-      <c r="AJ14" s="26"/>
-      <c r="AK14" s="4"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="25"/>
+      <c r="AI14" s="25"/>
+      <c r="AJ14" s="4"/>
     </row>
-    <row r="15" ht="14.75" spans="2:37">
+    <row r="15" spans="2:36">
       <c r="B15" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="4"/>
       <c r="F15" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>112</v>
+      <c r="G15" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>90</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
       <c r="U15" s="21"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
       <c r="AE15" s="25"/>
-      <c r="AF15" s="26"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="26"/>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="4"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
+      <c r="AJ15" s="4"/>
     </row>
-    <row r="16" ht="14.75" spans="2:37">
+    <row r="16" spans="2:36">
       <c r="B16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="4"/>
       <c r="F16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>115</v>
+      <c r="G16" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>91</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
       <c r="U16" s="21"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
       <c r="AE16" s="25"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="26"/>
-      <c r="AI16" s="26"/>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="4"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="25"/>
+      <c r="AJ16" s="4"/>
     </row>
-    <row r="17" ht="14.75" spans="2:37">
+    <row r="17" spans="2:36">
       <c r="B17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="4"/>
       <c r="F17" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>118</v>
+      <c r="G17" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="K17" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
       <c r="U17" s="21"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
       <c r="AE17" s="25"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="26"/>
-      <c r="AI17" s="26"/>
-      <c r="AJ17" s="26"/>
-      <c r="AK17" s="4"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="4"/>
     </row>
-    <row r="18" ht="14.75" spans="2:36">
+    <row r="18" spans="2:35">
       <c r="B18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>121</v>
+      <c r="G18" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="K18" s="18"/>
+        <v>77</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
       <c r="U18" s="21"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="25"/>
-      <c r="AD18" s="25"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
       <c r="AE18" s="25"/>
-      <c r="AF18" s="26"/>
-      <c r="AG18" s="26"/>
-      <c r="AH18" s="26"/>
-      <c r="AI18" s="26"/>
-      <c r="AJ18" s="26"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="25"/>
+      <c r="AI18" s="25"/>
     </row>
-    <row r="19" ht="14.75" spans="2:11">
-      <c r="B19" s="9"/>
-      <c r="K19" s="18"/>
+    <row r="19" spans="2:10">
+      <c r="B19" s="8"/>
+      <c r="J19" s="19"/>
     </row>
-    <row r="20" ht="14.75" spans="2:2">
-      <c r="B20" s="9"/>
+    <row r="20" spans="2:2">
+      <c r="B20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/pokemon.xlsx
+++ b/Excel/Datas/pokemon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="pokemon_table" sheetId="1" r:id="rId1"/>
@@ -299,7 +299,7 @@
     <t>Animal</t>
   </si>
   <si>
-    <t>Robot</t>
+    <t>机械</t>
   </si>
   <si>
     <t>枯木妖</t>
@@ -850,19 +850,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFDEE0E3"/>
       </left>
@@ -873,6 +860,19 @@
         <color rgb="FFDEE0E3"/>
       </top>
       <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
@@ -1138,23 +1138,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1163,49 +1163,49 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1534,12 +1534,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AJ20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
     <col min="3" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="67.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="67.5803571428571" customWidth="1"/>
     <col min="7" max="10" width="13.5" customWidth="1"/>
     <col min="26" max="26" width="11.875" customWidth="1"/>
     <col min="27" max="30" width="9.625" customWidth="1"/>
@@ -1843,7 +1843,7 @@
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" ht="17.55" spans="1:36">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -1856,16 +1856,16 @@
       <c r="D5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="6" t="s">
         <v>50</v>
       </c>
       <c r="I5" s="10"/>
@@ -1885,19 +1885,19 @@
       <c r="O5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="T5" s="18" t="s">
         <v>60</v>
       </c>
       <c r="U5" s="20" t="s">
@@ -1930,57 +1930,57 @@
       <c r="AD5" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="AE5" s="23" t="s">
+      <c r="AE5" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="AF5" s="23" t="s">
+      <c r="AF5" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="AG5" s="23" t="s">
+      <c r="AG5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="AH5" s="23" t="s">
+      <c r="AH5" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="AI5" s="23" t="s">
+      <c r="AI5" s="24" t="s">
         <v>75</v>
       </c>
       <c r="AJ5" s="26"/>
     </row>
-    <row r="6" spans="2:36">
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="17.55" spans="2:36">
+      <c r="B6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>340</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13">
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12">
         <v>450</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="19">
         <v>65</v>
       </c>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14">
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19">
         <v>90</v>
       </c>
       <c r="U6" s="21">
@@ -1992,13 +1992,13 @@
       <c r="Y6" s="21">
         <v>80</v>
       </c>
-      <c r="Z6" s="24">
+      <c r="Z6" s="23">
         <v>100</v>
       </c>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24">
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23">
         <v>160</v>
       </c>
       <c r="AE6" s="25">
@@ -2010,50 +2010,50 @@
       <c r="AI6" s="25">
         <v>30</v>
       </c>
-      <c r="AJ6" s="4"/>
+      <c r="AJ6" s="3"/>
     </row>
-    <row r="7" spans="2:36">
-      <c r="B7" s="6" t="s">
+    <row r="7" ht="17.55" spans="2:36">
+      <c r="B7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="13">
+      <c r="J7" s="14"/>
+      <c r="K7" s="12">
         <v>340</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13">
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12">
         <v>450</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="19">
         <v>65</v>
       </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14">
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19">
         <v>90</v>
       </c>
       <c r="U7" s="21">
@@ -2065,13 +2065,13 @@
       <c r="Y7" s="21">
         <v>80</v>
       </c>
-      <c r="Z7" s="24">
+      <c r="Z7" s="23">
         <v>100</v>
       </c>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24">
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23">
         <v>160</v>
       </c>
       <c r="AE7" s="25">
@@ -2083,605 +2083,605 @@
       <c r="AI7" s="25">
         <v>30</v>
       </c>
-      <c r="AJ7" s="4"/>
+      <c r="AJ7" s="3"/>
     </row>
-    <row r="8" spans="2:36">
-      <c r="B8" s="6" t="s">
+    <row r="8" ht="17.55" spans="2:36">
+      <c r="B8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
       <c r="U8" s="21"/>
       <c r="V8" s="21"/>
       <c r="W8" s="21"/>
       <c r="X8" s="21"/>
       <c r="Y8" s="21"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
       <c r="AE8" s="25"/>
       <c r="AF8" s="25"/>
       <c r="AG8" s="25"/>
       <c r="AH8" s="25"/>
       <c r="AI8" s="25"/>
-      <c r="AJ8" s="4"/>
+      <c r="AJ8" s="3"/>
     </row>
     <row r="9" spans="2:36">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
       <c r="U9" s="21"/>
       <c r="V9" s="21"/>
       <c r="W9" s="21"/>
       <c r="X9" s="21"/>
       <c r="Y9" s="21"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
       <c r="AE9" s="25"/>
       <c r="AF9" s="25"/>
       <c r="AG9" s="25"/>
       <c r="AH9" s="25"/>
       <c r="AI9" s="25"/>
-      <c r="AJ9" s="4"/>
+      <c r="AJ9" s="3"/>
     </row>
-    <row r="10" spans="2:36">
-      <c r="B10" s="6" t="s">
+    <row r="10" ht="17.55" spans="2:36">
+      <c r="B10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
       <c r="U10" s="21"/>
       <c r="V10" s="21"/>
       <c r="W10" s="21"/>
       <c r="X10" s="21"/>
       <c r="Y10" s="21"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="23"/>
+      <c r="AD10" s="23"/>
       <c r="AE10" s="25"/>
       <c r="AF10" s="25"/>
       <c r="AG10" s="25"/>
       <c r="AH10" s="25"/>
       <c r="AI10" s="25"/>
-      <c r="AJ10" s="4"/>
+      <c r="AJ10" s="3"/>
     </row>
-    <row r="11" spans="2:36">
-      <c r="B11" s="6" t="s">
+    <row r="11" ht="17.55" spans="2:36">
+      <c r="B11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="18"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
       <c r="U11" s="21"/>
       <c r="V11" s="21"/>
       <c r="W11" s="21"/>
       <c r="X11" s="21"/>
       <c r="Y11" s="21"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
+      <c r="Z11" s="23"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="23"/>
+      <c r="AD11" s="23"/>
       <c r="AE11" s="25"/>
       <c r="AF11" s="25"/>
       <c r="AG11" s="25"/>
       <c r="AH11" s="25"/>
       <c r="AI11" s="25"/>
-      <c r="AJ11" s="4"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="2:36">
-      <c r="B12" s="6" t="s">
+    <row r="12" ht="17.55" spans="2:36">
+      <c r="B12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
       <c r="U12" s="21"/>
       <c r="V12" s="21"/>
       <c r="W12" s="21"/>
       <c r="X12" s="21"/>
       <c r="Y12" s="21"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
       <c r="AE12" s="25"/>
       <c r="AF12" s="25"/>
       <c r="AG12" s="25"/>
       <c r="AH12" s="25"/>
       <c r="AI12" s="25"/>
-      <c r="AJ12" s="4"/>
+      <c r="AJ12" s="3"/>
     </row>
-    <row r="13" spans="2:36">
-      <c r="B13" s="6" t="s">
+    <row r="13" ht="17.55" spans="2:36">
+      <c r="B13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
       <c r="U13" s="21"/>
       <c r="V13" s="21"/>
       <c r="W13" s="21"/>
       <c r="X13" s="21"/>
       <c r="Y13" s="21"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
       <c r="AE13" s="25"/>
       <c r="AF13" s="25"/>
       <c r="AG13" s="25"/>
       <c r="AH13" s="25"/>
       <c r="AI13" s="25"/>
-      <c r="AJ13" s="4"/>
+      <c r="AJ13" s="3"/>
     </row>
-    <row r="14" spans="2:36">
-      <c r="B14" s="6" t="s">
+    <row r="14" ht="17.55" spans="2:36">
+      <c r="B14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
       <c r="U14" s="21"/>
       <c r="V14" s="21"/>
       <c r="W14" s="21"/>
       <c r="X14" s="21"/>
       <c r="Y14" s="21"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
       <c r="AE14" s="25"/>
       <c r="AF14" s="25"/>
       <c r="AG14" s="25"/>
       <c r="AH14" s="25"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="4"/>
+      <c r="AJ14" s="3"/>
     </row>
-    <row r="15" spans="2:36">
-      <c r="B15" s="6" t="s">
+    <row r="15" ht="17.55" spans="2:36">
+      <c r="B15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
       <c r="U15" s="21"/>
       <c r="V15" s="21"/>
       <c r="W15" s="21"/>
       <c r="X15" s="21"/>
       <c r="Y15" s="21"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
       <c r="AE15" s="25"/>
       <c r="AF15" s="25"/>
       <c r="AG15" s="25"/>
       <c r="AH15" s="25"/>
       <c r="AI15" s="25"/>
-      <c r="AJ15" s="4"/>
+      <c r="AJ15" s="3"/>
     </row>
-    <row r="16" spans="2:36">
-      <c r="B16" s="6" t="s">
+    <row r="16" ht="17.55" spans="2:36">
+      <c r="B16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
       <c r="U16" s="21"/>
       <c r="V16" s="21"/>
       <c r="W16" s="21"/>
       <c r="X16" s="21"/>
       <c r="Y16" s="21"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="23"/>
+      <c r="AD16" s="23"/>
       <c r="AE16" s="25"/>
       <c r="AF16" s="25"/>
       <c r="AG16" s="25"/>
       <c r="AH16" s="25"/>
       <c r="AI16" s="25"/>
-      <c r="AJ16" s="4"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="2:36">
-      <c r="B17" s="6" t="s">
+    <row r="17" ht="17.55" spans="2:36">
+      <c r="B17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
       <c r="U17" s="21"/>
       <c r="V17" s="21"/>
       <c r="W17" s="21"/>
       <c r="X17" s="21"/>
       <c r="Y17" s="21"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="23"/>
+      <c r="AD17" s="23"/>
       <c r="AE17" s="25"/>
       <c r="AF17" s="25"/>
       <c r="AG17" s="25"/>
       <c r="AH17" s="25"/>
       <c r="AI17" s="25"/>
-      <c r="AJ17" s="4"/>
+      <c r="AJ17" s="3"/>
     </row>
-    <row r="18" spans="2:35">
-      <c r="B18" s="6" t="s">
+    <row r="18" ht="17.55" spans="2:35">
+      <c r="B18" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
       <c r="U18" s="21"/>
       <c r="V18" s="21"/>
       <c r="W18" s="21"/>
       <c r="X18" s="21"/>
       <c r="Y18" s="21"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
       <c r="AE18" s="25"/>
       <c r="AF18" s="25"/>
       <c r="AG18" s="25"/>
       <c r="AH18" s="25"/>
       <c r="AI18" s="25"/>
     </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="8"/>
-      <c r="J19" s="19"/>
+    <row r="19" ht="17.55" spans="2:10">
+      <c r="B19" s="5"/>
+      <c r="J19" s="17"/>
     </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="8"/>
+    <row r="20" ht="17.55" spans="2:2">
+      <c r="B20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
